--- a/s122_emp_df_class.xlsx
+++ b/s122_emp_df_class.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P17"/>
+  <dimension ref="A1:Q48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -485,30 +485,35 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
+          <t>LineID</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>Position</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>MonthOTNew</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>YTDOTAvgNew</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>OJTCode</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>SkillName</t>
         </is>
@@ -517,7 +522,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>85278328</t>
+          <t>88866222</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -532,7 +537,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>27</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -552,48 +557,53 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>ME/MFO6.5-CN</t>
+          <t>ME/MFO6.11-CN</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>BSFA14</t>
+          <t>All</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>VI</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="n">
-        <v>46094</v>
-      </c>
-      <c r="M2" t="n">
-        <v>62</v>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Shopfloor leader</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="n">
+        <v>46108</v>
       </c>
       <c r="N2" t="n">
-        <v>34</v>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>OJT3116</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="O2" t="n">
+        <v>30.17</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>ECU VI</t>
+          <t>OJT3124</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Material Handling</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>85278328</t>
+          <t>88866222</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -608,7 +618,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>27</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -628,48 +638,53 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>ME/MFO6.5-CN</t>
+          <t>ME/MFO6.11-CN</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>BSFA14</t>
+          <t>All</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>VI</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="n">
-        <v>46094</v>
-      </c>
-      <c r="M3" t="n">
-        <v>62</v>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Shopfloor leader</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="n">
+        <v>46108</v>
       </c>
       <c r="N3" t="n">
-        <v>34</v>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>OJT3221</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="O3" t="n">
+        <v>30.17</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>DMC UV DAE and Damping ball</t>
+          <t>OJT3254</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>Testing LL</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>85278328</t>
+          <t>88866222</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -684,7 +699,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>27</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -704,48 +719,53 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>ME/MFO6.5-CN</t>
+          <t>ME/MFO6.11-CN</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>BSFA14</t>
+          <t>All</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>VI</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="n">
-        <v>46094</v>
-      </c>
-      <c r="M4" t="n">
-        <v>62</v>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Shopfloor leader</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>46108</v>
       </c>
       <c r="N4" t="n">
-        <v>34</v>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>OJT3132</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="O4" t="n">
+        <v>30.17</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lid and Hu sealing</t>
+          <t>OJT3632</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>Testing OP(Auto line)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>85278328</t>
+          <t>88866222</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -760,7 +780,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>27</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -780,48 +800,53 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>ME/MFO6.5-CN</t>
+          <t>ME/MFO6.11-CN</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>BSFA14</t>
+          <t>All</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>VI</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="n">
-        <v>46094</v>
-      </c>
-      <c r="M5" t="n">
-        <v>62</v>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Shopfloor leader</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="n">
+        <v>46108</v>
       </c>
       <c r="N5" t="n">
-        <v>34</v>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>OJT3207</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="O5" t="n">
+        <v>30.17</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>ME Assembly</t>
+          <t>OJT3103</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>Testing OP</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>85278328</t>
+          <t>88866222</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -836,7 +861,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>27</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -856,48 +881,53 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>ME/MFO6.5-CN</t>
+          <t>ME/MFO6.11-CN</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>BSFA14</t>
+          <t>All</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>VI</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="n">
-        <v>46094</v>
-      </c>
-      <c r="M6" t="n">
-        <v>62</v>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Shopfloor leader</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>46108</v>
       </c>
       <c r="N6" t="n">
-        <v>34</v>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>OJT3231</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="O6" t="n">
+        <v>30.17</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>DS ESD AOI and PCBA Assembly</t>
+          <t>OJT3102</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>Run In OP</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>85278328</t>
+          <t>88866222</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -912,7 +942,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>27</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -932,48 +962,53 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>ME/MFO6.5-CN</t>
+          <t>ME/MFO6.11-CN</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>BSFA14</t>
+          <t>All</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>VI</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="n">
-        <v>46094</v>
-      </c>
-      <c r="M7" t="n">
-        <v>62</v>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Shopfloor leader</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>46108</v>
       </c>
       <c r="N7" t="n">
-        <v>34</v>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>OJT3226</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="O7" t="n">
+        <v>30.17</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Coil assembly</t>
+          <t>OJT3105</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>Kardex_Testing</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>85278328</t>
+          <t>88869112</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -988,7 +1023,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>27</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1008,48 +1043,53 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>ME/MFO6.5-CN</t>
+          <t>ME/MFO6.11-CN</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>BSFA14</t>
+          <t>BSTesting10</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>VI</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="n">
-        <v>46094</v>
-      </c>
-      <c r="M8" t="n">
-        <v>62</v>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>46108</v>
       </c>
       <c r="N8" t="n">
-        <v>34</v>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>OJT3237</t>
-        </is>
+        <v>36</v>
+      </c>
+      <c r="O8" t="n">
+        <v>23.33</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Leakage test</t>
+          <t>OJT3102</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>Run In OP</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>88762156</t>
+          <t>88869112</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1064,7 +1104,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>27</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1084,48 +1124,53 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>ME/MFO6.5-CN</t>
+          <t>ME/MFO6.11-CN</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>BSFA14</t>
+          <t>BSTesting10</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>VI</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="n">
-        <v>46094</v>
-      </c>
-      <c r="M9" t="n">
-        <v>28</v>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v>46108</v>
       </c>
       <c r="N9" t="n">
-        <v>33.33</v>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>OJT3126</t>
-        </is>
+        <v>36</v>
+      </c>
+      <c r="O9" t="n">
+        <v>23.33</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Offline</t>
+          <t>OJT3103</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>Testing OP</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>88762156</t>
+          <t>85144856</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1140,7 +1185,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>27</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1160,48 +1205,53 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>ME/MFO6.5-CN</t>
+          <t>ME/MFO6.11-CN</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>BSFA14</t>
+          <t>BSTesting07</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>VI</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>46094</v>
-      </c>
-      <c r="M10" t="n">
-        <v>28</v>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="n">
+        <v>46108</v>
       </c>
       <c r="N10" t="n">
-        <v>33.33</v>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>OJT3116</t>
-        </is>
+        <v>12</v>
+      </c>
+      <c r="O10" t="n">
+        <v>32</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>ECU VI</t>
+          <t>OJT3103</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>Testing OP</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>88762156</t>
+          <t>85144856</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1216,7 +1266,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>27</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1236,48 +1286,53 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>ME/MFO6.5-CN</t>
+          <t>ME/MFO6.11-CN</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>BSFA14</t>
+          <t>BSTesting07</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>VI</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="n">
-        <v>46094</v>
-      </c>
-      <c r="M11" t="n">
-        <v>28</v>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="n">
+        <v>46108</v>
       </c>
       <c r="N11" t="n">
-        <v>33.33</v>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>OJT3237</t>
-        </is>
+        <v>12</v>
+      </c>
+      <c r="O11" t="n">
+        <v>32</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Leakage test</t>
+          <t>OJT3102</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>Run In OP</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>88762156</t>
+          <t>85144856</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1292,7 +1347,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>27</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1312,48 +1367,53 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>ME/MFO6.5-CN</t>
+          <t>ME/MFO6.11-CN</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>BSFA14</t>
+          <t>BSTesting07</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>VI</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="n">
-        <v>46094</v>
-      </c>
-      <c r="M12" t="n">
-        <v>28</v>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="n">
+        <v>46108</v>
       </c>
       <c r="N12" t="n">
-        <v>33.33</v>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>OJT3231</t>
-        </is>
+        <v>12</v>
+      </c>
+      <c r="O12" t="n">
+        <v>32</v>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>DS ESD AOI and PCBA Assembly</t>
+          <t>OJT3124</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>Material Handling</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>88762156</t>
+          <t>88695737</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1368,7 +1428,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>27</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1388,7 +1448,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>ME/MFO6.5-CN</t>
+          <t>ME/MFO6.11-CN</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1398,38 +1458,43 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>BSFA14</t>
+          <t>BSTesting15</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
           <t>VI</t>
         </is>
       </c>
-      <c r="L13" s="2" t="n">
-        <v>46094</v>
-      </c>
-      <c r="M13" t="n">
-        <v>28</v>
+      <c r="M13" s="2" t="n">
+        <v>46108</v>
       </c>
       <c r="N13" t="n">
-        <v>33.33</v>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>OJT3221</t>
-        </is>
+        <v>34</v>
+      </c>
+      <c r="O13" t="n">
+        <v>32</v>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>DMC UV DAE and Damping ball</t>
+          <t>OJT3632</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>Testing OP(Auto line)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>88762156</t>
+          <t>88695737</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1444,7 +1509,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>27</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1464,7 +1529,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>ME/MFO6.5-CN</t>
+          <t>ME/MFO6.11-CN</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1474,38 +1539,43 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>BSFA14</t>
+          <t>BSTesting15</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
           <t>VI</t>
         </is>
       </c>
-      <c r="L14" s="2" t="n">
-        <v>46094</v>
-      </c>
-      <c r="M14" t="n">
-        <v>28</v>
+      <c r="M14" s="2" t="n">
+        <v>46108</v>
       </c>
       <c r="N14" t="n">
-        <v>33.33</v>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>OJT3132</t>
-        </is>
+        <v>34</v>
+      </c>
+      <c r="O14" t="n">
+        <v>32</v>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lid and Hu sealing</t>
+          <t>OJT3103</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>Testing OP</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>88762156</t>
+          <t>88695737</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1520,7 +1590,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>27</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1540,7 +1610,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>ME/MFO6.5-CN</t>
+          <t>ME/MFO6.11-CN</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1550,38 +1620,43 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>BSFA14</t>
+          <t>BSTesting15</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
           <t>VI</t>
         </is>
       </c>
-      <c r="L15" s="2" t="n">
-        <v>46094</v>
-      </c>
-      <c r="M15" t="n">
-        <v>28</v>
+      <c r="M15" s="2" t="n">
+        <v>46108</v>
       </c>
       <c r="N15" t="n">
-        <v>33.33</v>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>OJT3226</t>
-        </is>
+        <v>34</v>
+      </c>
+      <c r="O15" t="n">
+        <v>32</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Coil assembly</t>
+          <t>OJT3260</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>PCBA VI</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>88900159</t>
+          <t>88722672</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1596,7 +1671,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>27</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1616,7 +1691,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>ME/MFO6.5-CN</t>
+          <t>ME/MFO6.11-CN</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1626,38 +1701,43 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>BSFA13</t>
+          <t>BSTesting05</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>MH</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="n">
-        <v>46094</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="n">
+        <v>46108</v>
       </c>
       <c r="N16" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>OJT3124</t>
-        </is>
+        <v>68</v>
+      </c>
+      <c r="O16" t="n">
+        <v>29.33</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Material Handling</t>
+          <t>OJT3103</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>Testing OP</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>88900159</t>
+          <t>88722672</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1672,7 +1752,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>27</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1692,7 +1772,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>ME/MFO6.5-CN</t>
+          <t>ME/MFO6.11-CN</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1702,31 +1782,2547 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>BSFA13</t>
+          <t>BSTesting05</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="N17" t="n">
+        <v>68</v>
+      </c>
+      <c r="O17" t="n">
+        <v>29.33</v>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>OJT3102</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>Run In OP</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>88481566</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>S122</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>ME/MOE6-CN</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>ME/MFO6.11-CN</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>女</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>BSTesting17</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
           <t>MH</t>
         </is>
       </c>
-      <c r="L17" s="2" t="n">
-        <v>46094</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>OJT3126</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>Offline</t>
+      <c r="M18" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="N18" t="n">
+        <v>34</v>
+      </c>
+      <c r="O18" t="n">
+        <v>34.17</v>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>OJT3124</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>Material Handling</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>88481566</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>S122</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>ME/MOE6-CN</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>ME/MFO6.11-CN</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>女</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>BSTesting17</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>MH</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="N19" t="n">
+        <v>34</v>
+      </c>
+      <c r="O19" t="n">
+        <v>34.17</v>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>OJT3105</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>Kardex_Testing</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>88481566</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>S122</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>ME/MOE6-CN</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>ME/MFO6.11-CN</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>女</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>BSTesting17</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>MH</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="N20" t="n">
+        <v>34</v>
+      </c>
+      <c r="O20" t="n">
+        <v>34.17</v>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>OJT3632</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>Testing OP(Auto line)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>88481566</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>S122</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>ME/MOE6-CN</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>ME/MFO6.11-CN</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>女</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>BSTesting17</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>MH</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="N21" t="n">
+        <v>34</v>
+      </c>
+      <c r="O21" t="n">
+        <v>34.17</v>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>OJT3102</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>Run In OP</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>88481566</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>S122</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>ME/MOE6-CN</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>ME/MFO6.11-CN</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>女</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>BSTesting17</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>MH</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="N22" t="n">
+        <v>34</v>
+      </c>
+      <c r="O22" t="n">
+        <v>34.17</v>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>OJT3260</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>PCBA VI</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>88481566</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>S122</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>ME/MOE6-CN</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>ME/MFO6.11-CN</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>女</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>BSTesting17</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>MH</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="N23" t="n">
+        <v>34</v>
+      </c>
+      <c r="O23" t="n">
+        <v>34.17</v>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>OJT3103</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>Testing OP</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>88900248</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>S122</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>ME/MOE6-CN</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>ME/MFO6.11-CN</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>BSTesting05</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="N24" t="n">
+        <v>28</v>
+      </c>
+      <c r="O24" t="n">
+        <v>22.67</v>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>OJT3221</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>DMC UV DAE and Damping ball</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>88900248</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>S122</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>ME/MOE6-CN</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>ME/MFO6.11-CN</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>BSTesting05</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="N25" t="n">
+        <v>28</v>
+      </c>
+      <c r="O25" t="n">
+        <v>22.67</v>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>OJT3124</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>Material Handling</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>88900248</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>S122</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>ME/MOE6-CN</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>ME/MFO6.11-CN</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>BSTesting05</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="N26" t="n">
+        <v>28</v>
+      </c>
+      <c r="O26" t="n">
+        <v>22.67</v>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>OJT3103</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>Testing OP</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>88900248</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>S122</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>ME/MOE6-CN</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>ME/MFO6.11-CN</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>BSTesting05</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="N27" t="n">
+        <v>28</v>
+      </c>
+      <c r="O27" t="n">
+        <v>22.67</v>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>OJT3232</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>Oven HT and Cooling</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>88900248</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>S122</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>ME/MOE6-CN</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>ME/MFO6.11-CN</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>BSTesting05</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="N28" t="n">
+        <v>28</v>
+      </c>
+      <c r="O28" t="n">
+        <v>22.67</v>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>OJT3231</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>DS ESD AOI and PCBA Assembly</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>88519624</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>S122</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>ME/MOE6-CN</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>ME/MFO6.11-CN</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>BSTesting17</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="N29" t="n">
+        <v>62</v>
+      </c>
+      <c r="O29" t="n">
+        <v>32</v>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>OJT3124</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>Material Handling</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>88519624</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>S122</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>ME/MOE6-CN</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>ME/MFO6.11-CN</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>BSTesting17</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="N30" t="n">
+        <v>62</v>
+      </c>
+      <c r="O30" t="n">
+        <v>32</v>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>OJT3103</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>Testing OP</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>88519624</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>S122</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>ME/MOE6-CN</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>ME/MFO6.11-CN</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>BSTesting17</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="N31" t="n">
+        <v>62</v>
+      </c>
+      <c r="O31" t="n">
+        <v>32</v>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>OJT3102</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>Run In OP</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>88519624</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>S122</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>ME/MOE6-CN</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>ME/MFO6.11-CN</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>BSTesting17</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="N32" t="n">
+        <v>62</v>
+      </c>
+      <c r="O32" t="n">
+        <v>32</v>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>OJT3632</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>Testing OP(Auto line)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>89210170</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>S122</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>ME/MOE6-CN</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>ME/MFO6.11-CN</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>BSTesting16</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="N33" t="n">
+        <v>70</v>
+      </c>
+      <c r="O33" t="n">
+        <v>32</v>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>OJT3632</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>Testing OP(Auto line)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>89210170</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>S122</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>ME/MOE6-CN</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>ME/MFO6.11-CN</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>BSTesting16</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="N34" t="n">
+        <v>70</v>
+      </c>
+      <c r="O34" t="n">
+        <v>32</v>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>OJT3102</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>Run In OP</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>89210170</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>S122</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>ME/MOE6-CN</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>ME/MFO6.11-CN</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>BSTesting16</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="N35" t="n">
+        <v>70</v>
+      </c>
+      <c r="O35" t="n">
+        <v>32</v>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>OJT3103</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>Testing OP</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>89091058</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>S122</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>ME/MOE6-CN</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>ME/MFO6.11-CN</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>BSTesting09</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="N36" t="n">
+        <v>38</v>
+      </c>
+      <c r="O36" t="n">
+        <v>29.17</v>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>OJT3632</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>Testing OP(Auto line)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>89091058</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>S122</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>ME/MOE6-CN</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>ME/MFO6.11-CN</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>BSTesting09</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="N37" t="n">
+        <v>38</v>
+      </c>
+      <c r="O37" t="n">
+        <v>29.17</v>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>OJT3102</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>Run In OP</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>89091058</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>S122</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>ME/MOE6-CN</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>ME/MFO6.11-CN</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>BSTesting09</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="N38" t="n">
+        <v>38</v>
+      </c>
+      <c r="O38" t="n">
+        <v>29.17</v>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>OJT3103</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>Testing OP</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>89271096</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>S122</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>ME/MOE6-CN</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>ME/MFO6.11-CN</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>BSTesting07</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="N39" t="n">
+        <v>34</v>
+      </c>
+      <c r="O39" t="n">
+        <v>34.67</v>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>OJT3102</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>Run In OP</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>89271096</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>S122</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>ME/MOE6-CN</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>ME/MFO6.11-CN</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>BSTesting07</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="N40" t="n">
+        <v>34</v>
+      </c>
+      <c r="O40" t="n">
+        <v>34.67</v>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>OJT3103</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>Testing OP</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>89108932</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>S122</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>ME/MOE6-CN</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>ME/MFO6.11-CN</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>BSRunin04</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="N41" t="n">
+        <v>28</v>
+      </c>
+      <c r="O41" t="n">
+        <v>22.67</v>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>OJT3124</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>Material Handling</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>89108932</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>S122</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>ME/MOE6-CN</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>ME/MFO6.11-CN</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>BSRunin04</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="N42" t="n">
+        <v>28</v>
+      </c>
+      <c r="O42" t="n">
+        <v>22.67</v>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>OJT3102</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>Run In OP</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>89108932</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>S122</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>ME/MOE6-CN</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>ME/MFO6.11-CN</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>BSRunin04</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="N43" t="n">
+        <v>28</v>
+      </c>
+      <c r="O43" t="n">
+        <v>22.67</v>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>OJT3105</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>Kardex_Testing</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>89108932</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>S122</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>ME/MOE6-CN</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>ME/MFO6.11-CN</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>BSRunin04</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="N44" t="n">
+        <v>28</v>
+      </c>
+      <c r="O44" t="n">
+        <v>22.67</v>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>OJT3103</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>Testing OP</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>89108932</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>S122</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>ME/MOE6-CN</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>ME/MFO6.11-CN</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>BSRunin04</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="N45" t="n">
+        <v>28</v>
+      </c>
+      <c r="O45" t="n">
+        <v>22.67</v>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>OJT3632</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>Testing OP(Auto line)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>88786648</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>S122</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>ME/MOE6-CN</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>ME/MFO6.11-CN</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>BSTesting08</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="N46" t="n">
+        <v>38</v>
+      </c>
+      <c r="O46" t="n">
+        <v>22.67</v>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>OJT3102</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>Run In OP</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>88786648</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>S122</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>ME/MOE6-CN</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>ME/MFO6.11-CN</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>BSTesting08</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="N47" t="n">
+        <v>38</v>
+      </c>
+      <c r="O47" t="n">
+        <v>22.67</v>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>OJT3103</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>Testing OP</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>88786648</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>S122</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>ME/MOE6-CN</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>ME/MFO6.11-CN</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>BSTesting08</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>OP</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="N48" t="n">
+        <v>38</v>
+      </c>
+      <c r="O48" t="n">
+        <v>22.67</v>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>OJT3632</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>Testing OP(Auto line)</t>
         </is>
       </c>
     </row>

--- a/s122_emp_df_class.xlsx
+++ b/s122_emp_df_class.xlsx
@@ -1818,7 +1818,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>88481566</t>
+          <t>88900248</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1858,48 +1858,48 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>BSTesting17</t>
+          <t>BSTesting05</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="M18" s="2" t="n">
         <v>46108</v>
       </c>
       <c r="N18" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="O18" t="n">
-        <v>34.17</v>
+        <v>22.67</v>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>OJT3124</t>
+          <t>OJT3221</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>Material Handling</t>
+          <t>DMC UV DAE and Damping ball</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>88481566</t>
+          <t>88900248</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1939,48 +1939,48 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>BSTesting17</t>
+          <t>BSTesting05</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="M19" s="2" t="n">
         <v>46108</v>
       </c>
       <c r="N19" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="O19" t="n">
-        <v>34.17</v>
+        <v>22.67</v>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>OJT3105</t>
+          <t>OJT3124</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>Kardex_Testing</t>
+          <t>Material Handling</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>88481566</t>
+          <t>88900248</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2020,48 +2020,48 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>BSTesting17</t>
+          <t>BSTesting05</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="M20" s="2" t="n">
         <v>46108</v>
       </c>
       <c r="N20" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="O20" t="n">
-        <v>34.17</v>
+        <v>22.67</v>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>OJT3632</t>
+          <t>OJT3103</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>Testing OP(Auto line)</t>
+          <t>Testing OP</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>88481566</t>
+          <t>88900248</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2101,48 +2101,48 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>BSTesting17</t>
+          <t>BSTesting05</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="M21" s="2" t="n">
         <v>46108</v>
       </c>
       <c r="N21" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="O21" t="n">
-        <v>34.17</v>
+        <v>22.67</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>OJT3102</t>
+          <t>OJT3232</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>Run In OP</t>
+          <t>Oven HT and Cooling</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>88481566</t>
+          <t>88900248</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2182,41 +2182,41 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>男</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>BSTesting17</t>
+          <t>BSTesting05</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>MH</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="M22" s="2" t="n">
         <v>46108</v>
       </c>
       <c r="N22" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="O22" t="n">
-        <v>34.17</v>
+        <v>22.67</v>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>OJT3260</t>
+          <t>OJT3231</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>PCBA VI</t>
+          <t>DS ESD AOI and PCBA Assembly</t>
         </is>
       </c>
     </row>
@@ -2292,19 +2292,19 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>OJT3103</t>
+          <t>OJT3124</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>Testing OP</t>
+          <t>Material Handling</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>88900248</t>
+          <t>88481566</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2344,48 +2344,48 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>BSTesting05</t>
+          <t>BSTesting17</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>23</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="M24" s="2" t="n">
         <v>46108</v>
       </c>
       <c r="N24" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="O24" t="n">
-        <v>22.67</v>
+        <v>34.17</v>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>OJT3221</t>
+          <t>OJT3105</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>DMC UV DAE and Damping ball</t>
+          <t>Kardex_Testing</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>88900248</t>
+          <t>88481566</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2425,48 +2425,48 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>BSTesting05</t>
+          <t>BSTesting17</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>23</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="M25" s="2" t="n">
         <v>46108</v>
       </c>
       <c r="N25" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="O25" t="n">
-        <v>22.67</v>
+        <v>34.17</v>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>OJT3124</t>
+          <t>OJT3632</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>Material Handling</t>
+          <t>Testing OP(Auto line)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>88900248</t>
+          <t>88481566</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2506,48 +2506,48 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>BSTesting05</t>
+          <t>BSTesting17</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>23</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="M26" s="2" t="n">
         <v>46108</v>
       </c>
       <c r="N26" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="O26" t="n">
-        <v>22.67</v>
+        <v>34.17</v>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>OJT3103</t>
+          <t>OJT3102</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>Testing OP</t>
+          <t>Run In OP</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>88900248</t>
+          <t>88481566</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2587,48 +2587,48 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>BSTesting05</t>
+          <t>BSTesting17</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>23</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="M27" s="2" t="n">
         <v>46108</v>
       </c>
       <c r="N27" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="O27" t="n">
-        <v>22.67</v>
+        <v>34.17</v>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>OJT3232</t>
+          <t>OJT3260</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>Oven HT and Cooling</t>
+          <t>PCBA VI</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>88900248</t>
+          <t>88481566</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2668,41 +2668,41 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>女</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>BSTesting05</t>
+          <t>BSTesting17</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>23</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>MH</t>
         </is>
       </c>
       <c r="M28" s="2" t="n">
         <v>46108</v>
       </c>
       <c r="N28" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="O28" t="n">
-        <v>22.67</v>
+        <v>34.17</v>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>OJT3231</t>
+          <t>OJT3103</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>DS ESD AOI and PCBA Assembly</t>
+          <t>Testing OP</t>
         </is>
       </c>
     </row>
@@ -3276,7 +3276,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>89091058</t>
+          <t>88786648</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3321,12 +3321,12 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>BSTesting09</t>
+          <t>BSTesting08</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -3341,23 +3341,23 @@
         <v>38</v>
       </c>
       <c r="O36" t="n">
-        <v>29.17</v>
+        <v>22.67</v>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>OJT3632</t>
+          <t>OJT3102</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>Testing OP(Auto line)</t>
+          <t>Run In OP</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>89091058</t>
+          <t>88786648</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3402,12 +3402,12 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>BSTesting09</t>
+          <t>BSTesting08</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -3422,23 +3422,23 @@
         <v>38</v>
       </c>
       <c r="O37" t="n">
-        <v>29.17</v>
+        <v>22.67</v>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>OJT3102</t>
+          <t>OJT3103</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>Run In OP</t>
+          <t>Testing OP</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>89091058</t>
+          <t>88786648</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>BSTesting09</t>
+          <t>BSTesting08</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -3503,23 +3503,23 @@
         <v>38</v>
       </c>
       <c r="O38" t="n">
-        <v>29.17</v>
+        <v>22.67</v>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>OJT3103</t>
+          <t>OJT3632</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>Testing OP</t>
+          <t>Testing OP(Auto line)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>89271096</t>
+          <t>89091058</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>BSTesting07</t>
+          <t>BSTesting09</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -3581,26 +3581,26 @@
         <v>46108</v>
       </c>
       <c r="N39" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="O39" t="n">
-        <v>34.67</v>
+        <v>29.17</v>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>OJT3102</t>
+          <t>OJT3632</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>Run In OP</t>
+          <t>Testing OP(Auto line)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>89271096</t>
+          <t>89091058</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3645,12 +3645,12 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>BSTesting07</t>
+          <t>BSTesting09</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3662,26 +3662,26 @@
         <v>46108</v>
       </c>
       <c r="N40" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="O40" t="n">
-        <v>34.67</v>
+        <v>29.17</v>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>OJT3103</t>
+          <t>OJT3102</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>Testing OP</t>
+          <t>Run In OP</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>89108932</t>
+          <t>89091058</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>BSRunin04</t>
+          <t>BSTesting09</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3743,26 +3743,26 @@
         <v>46108</v>
       </c>
       <c r="N41" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="O41" t="n">
-        <v>22.67</v>
+        <v>29.17</v>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>OJT3124</t>
+          <t>OJT3103</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>Material Handling</t>
+          <t>Testing OP</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>89108932</t>
+          <t>89271096</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3807,12 +3807,12 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>BSRunin04</t>
+          <t>BSTesting07</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3824,10 +3824,10 @@
         <v>46108</v>
       </c>
       <c r="N42" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="O42" t="n">
-        <v>22.67</v>
+        <v>34.67</v>
       </c>
       <c r="P42" t="inlineStr">
         <is>
@@ -3843,7 +3843,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>89108932</t>
+          <t>89271096</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3888,12 +3888,12 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>BSRunin04</t>
+          <t>BSTesting07</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3905,19 +3905,19 @@
         <v>46108</v>
       </c>
       <c r="N43" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="O43" t="n">
-        <v>22.67</v>
+        <v>34.67</v>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>OJT3105</t>
+          <t>OJT3103</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>Kardex_Testing</t>
+          <t>Testing OP</t>
         </is>
       </c>
     </row>
@@ -3993,12 +3993,12 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>OJT3103</t>
+          <t>OJT3124</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>Testing OP</t>
+          <t>Material Handling</t>
         </is>
       </c>
     </row>
@@ -4074,19 +4074,19 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>OJT3632</t>
+          <t>OJT3102</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>Testing OP(Auto line)</t>
+          <t>Run In OP</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>88786648</t>
+          <t>89108932</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4131,12 +4131,12 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>BSTesting08</t>
+          <t>BSRunin04</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -4148,26 +4148,26 @@
         <v>46108</v>
       </c>
       <c r="N46" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="O46" t="n">
         <v>22.67</v>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>OJT3102</t>
+          <t>OJT3105</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>Run In OP</t>
+          <t>Kardex_Testing</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>88786648</t>
+          <t>89108932</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>BSTesting08</t>
+          <t>BSRunin04</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -4229,7 +4229,7 @@
         <v>46108</v>
       </c>
       <c r="N47" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="O47" t="n">
         <v>22.67</v>
@@ -4248,7 +4248,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>88786648</t>
+          <t>89108932</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4293,12 +4293,12 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>BSTesting08</t>
+          <t>BSRunin04</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -4310,7 +4310,7 @@
         <v>46108</v>
       </c>
       <c r="N48" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="O48" t="n">
         <v>22.67</v>
